--- a/CoforgeSeleniumTesting/HybridSeleniumFrameWork/TestData/TestData.xlsx
+++ b/CoforgeSeleniumTesting/HybridSeleniumFrameWork/TestData/TestData.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0377cb67aaf17726/Documents/GitHub/Kunal-Testing-Assignments/CoforgeSeleniumTesting/HybridSeleniumFrameWork/TestData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_F25DC773A252ABDACC1048B5219A54FA5ADE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64A76FAE-F1A6-4F30-ADBD-89113432421B}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="11_F25DC773A252ABDACC1048B5219A54FA5ADE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B0DB151-CE69-45E8-8524-32C440596FD1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="LoginHRM" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -83,6 +83,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
